--- a/meta/program/BlancoRestGeneratorKtTelegramProcessStructure.xlsx
+++ b/meta/program/BlancoRestGeneratorKtTelegramProcessStructure.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tueda/data/webstorm/blanco/blancoRestGeneratorKt/meta/program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F010F987-13AE-E148-BD79-1A2DD755100A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C796A2F0-07AE-6E43-BA7B-7BC00B026998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6880" yWindow="500" windowWidth="22260" windowHeight="17480" tabRatio="640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="101">
   <si>
     <t>バリューオブジェクト定義書</t>
   </si>
@@ -542,6 +542,21 @@
     <rPh sb="19" eb="21">
       <t xml:space="preserve">キョウツウ </t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>java.util.Map&lt;java.lang.String, blanco.restgeneratorkt.valueobject.BlancoRestGeneratorKtTelegramProcessMethodMetaInfoStructure&gt;</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>メソッドメタ情報</t>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">ジョウホウ </t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>methodMetaInfoMap</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -595,7 +610,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1001,11 +1016,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="hair">
+        <color indexed="8"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1143,76 +1173,79 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1606,7 +1639,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="000000">
@@ -1650,7 +1683,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{AF507438-7753-43e0-B8FC-AC1667EBCBE1}">
-            <a14:hiddenEffects xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
               <a:effectLst>
                 <a:outerShdw blurRad="63500" dist="38099" dir="2700000" algn="ctr" rotWithShape="0">
                   <a:srgbClr val="000000">
@@ -1675,7 +1708,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -1846,23 +1879,23 @@
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="63" t="s">
+      <c r="A19" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="65" t="s">
+      <c r="B19" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="67"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="68"/>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="63"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="67"/>
+      <c r="A20" s="65"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="68"/>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6">
@@ -1899,29 +1932,29 @@
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A25" s="63" t="s">
+      <c r="A25" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="64" t="s">
+      <c r="C25" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="64" t="s">
+      <c r="D25" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="64" t="s">
+      <c r="E25" s="73" t="s">
         <v>7</v>
       </c>
       <c r="F25" s="26"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="63"/>
-      <c r="B26" s="63"/>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
+      <c r="A26" s="65"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
       <c r="F26" s="27"/>
     </row>
     <row r="27" spans="1:6">
@@ -1959,7 +1992,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="30">
-        <f t="shared" ref="A29:A55" si="0">A28+1</f>
+        <f t="shared" ref="A29:A56" si="0">A28+1</f>
         <v>3</v>
       </c>
       <c r="B29" s="31" t="s">
@@ -1969,10 +2002,10 @@
         <v>23</v>
       </c>
       <c r="D29" s="32"/>
-      <c r="E29" s="59" t="s">
+      <c r="E29" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="F29" s="60"/>
+      <c r="F29" s="70"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="30">
@@ -1986,10 +2019,10 @@
         <v>30</v>
       </c>
       <c r="D30" s="43"/>
-      <c r="E30" s="57" t="s">
+      <c r="E30" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="58"/>
+      <c r="F30" s="55"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="30">
@@ -2037,10 +2070,10 @@
         <v>30</v>
       </c>
       <c r="D33" s="32"/>
-      <c r="E33" s="61" t="s">
+      <c r="E33" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="F33" s="62"/>
+      <c r="F33" s="72"/>
     </row>
     <row r="34" spans="1:7" ht="50" customHeight="1">
       <c r="A34" s="30">
@@ -2054,10 +2087,10 @@
         <v>30</v>
       </c>
       <c r="D34" s="32"/>
-      <c r="E34" s="61" t="s">
+      <c r="E34" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="F34" s="62"/>
+      <c r="F34" s="72"/>
     </row>
     <row r="35" spans="1:7" ht="45">
       <c r="A35" s="30">
@@ -2073,10 +2106,10 @@
       <c r="D35" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="E35" s="51" t="s">
+      <c r="E35" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="F35" s="52"/>
+      <c r="F35" s="53"/>
       <c r="G35"/>
     </row>
     <row r="36" spans="1:7" ht="45">
@@ -2093,10 +2126,10 @@
       <c r="D36" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="51" t="s">
+      <c r="E36" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="F36" s="52"/>
+      <c r="F36" s="53"/>
       <c r="G36"/>
     </row>
     <row r="37" spans="1:7" ht="45">
@@ -2113,10 +2146,10 @@
       <c r="D37" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="E37" s="51" t="s">
+      <c r="E37" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="F37" s="52"/>
+      <c r="F37" s="53"/>
       <c r="G37"/>
     </row>
     <row r="38" spans="1:7">
@@ -2133,10 +2166,10 @@
       <c r="D38" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="E38" s="57" t="s">
+      <c r="E38" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="58"/>
+      <c r="F38" s="55"/>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="30">
@@ -2152,10 +2185,10 @@
       <c r="D39" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="57" t="s">
+      <c r="E39" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="F39" s="58"/>
+      <c r="F39" s="55"/>
     </row>
     <row r="40" spans="1:7" ht="15">
       <c r="A40" s="30">
@@ -2171,10 +2204,10 @@
       <c r="D40" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="E40" s="53" t="s">
+      <c r="E40" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="54"/>
+      <c r="F40" s="62"/>
       <c r="G40"/>
     </row>
     <row r="41" spans="1:7" ht="15">
@@ -2189,10 +2222,10 @@
         <v>23</v>
       </c>
       <c r="D41" s="46"/>
-      <c r="E41" s="53" t="s">
+      <c r="E41" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="54"/>
+      <c r="F41" s="62"/>
       <c r="G41"/>
     </row>
     <row r="42" spans="1:7" ht="45" customHeight="1">
@@ -2209,10 +2242,10 @@
       <c r="D42" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="53" t="s">
+      <c r="E42" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="F42" s="72"/>
+      <c r="F42" s="61"/>
       <c r="G42"/>
     </row>
     <row r="43" spans="1:7" ht="45" customHeight="1">
@@ -2229,10 +2262,10 @@
       <c r="D43" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="E43" s="53" t="s">
+      <c r="E43" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="F43" s="72"/>
+      <c r="F43" s="61"/>
       <c r="G43"/>
     </row>
     <row r="44" spans="1:7" ht="45">
@@ -2249,10 +2282,10 @@
       <c r="D44" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="E44" s="53" t="s">
+      <c r="E44" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="F44" s="54"/>
+      <c r="F44" s="62"/>
       <c r="G44"/>
     </row>
     <row r="45" spans="1:7" ht="45">
@@ -2269,10 +2302,10 @@
       <c r="D45" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="E45" s="55" t="s">
+      <c r="E45" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="F45" s="56"/>
+      <c r="F45" s="75"/>
       <c r="G45"/>
     </row>
     <row r="46" spans="1:7" ht="90">
@@ -2289,10 +2322,10 @@
       <c r="D46" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="E46" s="73" t="s">
+      <c r="E46" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="F46" s="74"/>
+      <c r="F46" s="64"/>
       <c r="G46"/>
     </row>
     <row r="47" spans="1:7" ht="105" customHeight="1">
@@ -2309,10 +2342,10 @@
       <c r="D47" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E47" s="68" t="s">
+      <c r="E47" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="69"/>
+      <c r="F47" s="57"/>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="30">
@@ -2360,10 +2393,10 @@
         <v>30</v>
       </c>
       <c r="D50" s="49"/>
-      <c r="E50" s="53" t="s">
+      <c r="E50" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="F50" s="54"/>
+      <c r="F50" s="62"/>
       <c r="G50"/>
     </row>
     <row r="51" spans="1:7" ht="15">
@@ -2378,10 +2411,10 @@
         <v>30</v>
       </c>
       <c r="D51" s="49"/>
-      <c r="E51" s="53" t="s">
+      <c r="E51" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="F51" s="54"/>
+      <c r="F51" s="62"/>
       <c r="G51"/>
     </row>
     <row r="52" spans="1:7" ht="15">
@@ -2396,10 +2429,10 @@
         <v>30</v>
       </c>
       <c r="D52" s="49"/>
-      <c r="E52" s="53" t="s">
+      <c r="E52" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="F52" s="54"/>
+      <c r="F52" s="62"/>
       <c r="G52"/>
     </row>
     <row r="53" spans="1:7" ht="75" customHeight="1">
@@ -2416,10 +2449,10 @@
       <c r="D53" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E53" s="70" t="s">
+      <c r="E53" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="F53" s="71"/>
+      <c r="F53" s="59"/>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="30">
@@ -2435,10 +2468,10 @@
       <c r="D54" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="E54" s="57" t="s">
+      <c r="E54" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="F54" s="58"/>
+      <c r="F54" s="55"/>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="30">
@@ -2454,38 +2487,110 @@
       <c r="D55" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="E55" s="57" t="s">
+      <c r="E55" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="F55" s="58"/>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="30"/>
-      <c r="B56" s="45"/>
-      <c r="C56" s="46"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="51"/>
-      <c r="F56" s="52"/>
+      <c r="F55" s="55"/>
+    </row>
+    <row r="56" spans="1:7" ht="90">
+      <c r="A56" s="30">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B56" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C56" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="F56" s="64"/>
       <c r="G56"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="44"/>
-      <c r="B57" s="31"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="33"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="48"/>
+      <c r="C57" s="46"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="64"/>
+      <c r="G57"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="22"/>
-      <c r="B58" s="34"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="35"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="48"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="63"/>
+      <c r="F58" s="64"/>
+      <c r="G58"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="30"/>
+      <c r="B59" s="48"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="63"/>
+      <c r="F59" s="64"/>
+      <c r="G59"/>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="30"/>
+      <c r="B60" s="48"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="52"/>
+      <c r="F60" s="53"/>
+      <c r="G60"/>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="44"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="33"/>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="22"/>
+      <c r="B62" s="34"/>
+      <c r="C62" s="23"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="38">
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
     <mergeCell ref="E36:F36"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="E39:F39"/>
@@ -2499,30 +2604,9 @@
     <mergeCell ref="E41:F41"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="E43:F43"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E55:F55"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
-  <dataValidations count="5">
+  <dataValidations disablePrompts="1" count="5">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C13" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>adjustDefaultValue</formula1>
       <formula2>0</formula2>
